--- a/d_00_ed_uced.xlsx
+++ b/d_00_ed_uced.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PriyeshGosai\Github\ich_course_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF36C5CB-9A0F-4A83-9B9D-DF52EE1C5232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1F7F2B-116D-4100-A2E9-C05C8AC7E2F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{C4103D47-9B4C-4342-BFC4-2639338CB718}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="420" xr2:uid="{C4103D47-9B4C-4342-BFC4-2639338CB718}"/>
   </bookViews>
   <sheets>
     <sheet name="Calculation 1" sheetId="1" r:id="rId1"/>
